--- a/outputs/unpatched_model_comparison.xlsx
+++ b/outputs/unpatched_model_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,352 +456,480 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>cv_aug_r2_std</t>
+          <t>test_mape</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>cv_baseline_mape</t>
+          <t>test_mape_std</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>cv_baseline_r2</t>
+          <t>test_r2</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>test_mape</t>
+          <t>test_r2_std</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>test_r2</t>
+          <t>test_mape_base</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>test_mape_base_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>test_r2_base</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>aug_delta_mape</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>aug_paired_p</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"length_scale": 1.0, "noise": 1.0, "alpha": 1e-06}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.809041514992714</v>
+        <v>6.966905505521997</v>
       </c>
       <c r="D2" t="n">
-        <v>2.592952377065467</v>
+        <v>1.883068303448421</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9553568720817566</v>
+        <v>0.9332498384841745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02131773598063856</v>
+        <v>6.966908984050929</v>
       </c>
       <c r="G2" t="n">
-        <v>6.103544775396585</v>
+        <v>1.883068252139846</v>
       </c>
       <c r="H2" t="n">
-        <v>0.932583487033844</v>
+        <v>0.9332497238294518</v>
       </c>
       <c r="I2" t="n">
-        <v>3.17726843059063</v>
+        <v>0.03266236906771333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9936057329177856</v>
+        <v>3.332931691463179</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7558007707987378</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9833864401901188</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.633977292587749</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01020827967719814</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.374360138310176</v>
+        <v>5.50665371119976</v>
       </c>
       <c r="D3" t="n">
-        <v>2.241938914283633</v>
+        <v>1.034068434070141</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9579787810706442</v>
+        <v>0.9612958550453186</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01974789372605842</v>
+        <v>7.127603143453598</v>
       </c>
       <c r="G3" t="n">
-        <v>4.960404359912187</v>
+        <v>1.498039842117023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9677366581630233</v>
+        <v>0.9359500527381897</v>
       </c>
       <c r="I3" t="n">
-        <v>4.480022839507727</v>
+        <v>0.04584726768337579</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9835758270585994</v>
+        <v>10.30082747340202</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.746842342734349</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8805586457252502</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-3.173224329948425</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.372294573087768</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"degree": 2, "alpha": 0.1}</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.906445611374796</v>
+        <v>7.511232420802116</v>
       </c>
       <c r="D4" t="n">
-        <v>6.047002511883136</v>
+        <v>1.437879477724647</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9077615886543688</v>
+        <v>0.9307578563690185</v>
       </c>
       <c r="F4" t="n">
-        <v>0.101456311340782</v>
+        <v>7.790737897157669</v>
       </c>
       <c r="G4" t="n">
-        <v>12.19192329935404</v>
+        <v>1.719178754521296</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8501760244874603</v>
+        <v>0.9245170593261719</v>
       </c>
       <c r="I4" t="n">
-        <v>4.560881421007887</v>
+        <v>0.04027702768590326</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9877138623158406</v>
+        <v>4.353821724653244</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.442751922629861</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9764046192169189</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.436916172504425</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.05189409173984656</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>KAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"length_scale": 1.0, "noise": 0.1, "alpha": 1e-06}</t>
+          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.349227618489612</v>
+        <v>8.409733325242996</v>
       </c>
       <c r="D5" t="n">
-        <v>3.155697444712513</v>
+        <v>2.163743933716832</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9618532787247716</v>
+        <v>0.8989832401275635</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02587004599348607</v>
+        <v>8.409741967916489</v>
       </c>
       <c r="G5" t="n">
-        <v>3.148278048190835</v>
+        <v>2.163752069414842</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9891886577085314</v>
+        <v>0.8989832878112793</v>
       </c>
       <c r="I5" t="n">
-        <v>4.824655986643232</v>
+        <v>0.06656984490098032</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9844428731966401</v>
+        <v>6.677707582712173</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.995546916575643</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9408537983894348</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.732034385204315</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3997035563060538</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.1}</t>
+          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.38854438964885</v>
+        <v>8.523493436924294</v>
       </c>
       <c r="D6" t="n">
-        <v>2.625084158092837</v>
+        <v>0.7234285220634195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9459945294553936</v>
+        <v>0.9247806284409418</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02547386098191972</v>
+        <v>8.752054807958197</v>
       </c>
       <c r="G6" t="n">
-        <v>19.68436447361526</v>
+        <v>0.7783789910879163</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6720184026617219</v>
+        <v>0.9239478992380205</v>
       </c>
       <c r="I6" t="n">
-        <v>4.99369618045074</v>
+        <v>0.03257870052170608</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9877609240086934</v>
+        <v>7.04312150055456</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.164237514322964</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9382990134204571</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.708933307403638</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1941687925606237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.782866910099983</v>
+        <v>9.023765138171095</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9938503593368969</v>
+        <v>2.659086924221477</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9690348982810975</v>
+        <v>0.8796402007102602</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02043911821068023</v>
+        <v>9.812965574971736</v>
       </c>
       <c r="G7" t="n">
-        <v>9.231513254344463</v>
+        <v>2.890968124235552</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8955170035362243</v>
+        <v>0.8664535919218267</v>
       </c>
       <c r="I7" t="n">
-        <v>5.366401746869087</v>
+        <v>0.07005426531886932</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9813423156738281</v>
+        <v>7.079140664106073</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.138178177781637</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9170059534992353</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.733824910865663</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.10047533643915</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 10.0}</t>
+          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.939909070730209</v>
+        <v>10.16758047219126</v>
       </c>
       <c r="D8" t="n">
-        <v>2.37798514646904</v>
+        <v>2.751599637391529</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9651089668273926</v>
+        <v>0.8677814432588505</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01706608492677041</v>
+        <v>10.12893668727058</v>
       </c>
       <c r="G8" t="n">
-        <v>8.706861287355423</v>
+        <v>2.690217638750525</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9406991958618164</v>
+        <v>0.868693204229903</v>
       </c>
       <c r="I8" t="n">
-        <v>6.383168697357178</v>
+        <v>0.07630655483827697</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9844565987586975</v>
+        <v>13.30679895330586</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.226862329003885</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7762184356299575</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-3.177862266035284</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00145940067976251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.1, "gamma": "scale"}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.742779328810039</v>
+        <v>10.07374130189419</v>
       </c>
       <c r="D9" t="n">
-        <v>2.684947342742644</v>
+        <v>4.258609807149377</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9322926930797368</v>
+        <v>0.8220464706420898</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03578456290272591</v>
+        <v>10.59895642101765</v>
       </c>
       <c r="G9" t="n">
-        <v>8.097551172844394</v>
+        <v>4.42852571075956</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9169343052050634</v>
+        <v>0.823086416721344</v>
       </c>
       <c r="I9" t="n">
-        <v>7.45713942345345</v>
+        <v>0.1422591865219926</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9708460630541239</v>
+        <v>6.884058862924576</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.114538057231541</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9045770764350891</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.714897558093071</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1426069640955435</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KAN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
+          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.282314226031303</v>
+        <v>10.57922530733718</v>
       </c>
       <c r="D10" t="n">
-        <v>2.400404767574668</v>
+        <v>2.647080088244683</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9452667713165284</v>
+        <v>0.8571329470227113</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04004188309400268</v>
+        <v>10.98316240735477</v>
       </c>
       <c r="G10" t="n">
-        <v>8.27773816883564</v>
+        <v>3.265886853694015</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9169708490371704</v>
+        <v>0.8389217431951256</v>
       </c>
       <c r="I10" t="n">
-        <v>8.245276659727097</v>
+        <v>0.1114494564659487</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9706928730010986</v>
+        <v>15.7521397003287</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.426251243278281</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7259022320902361</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-4.768977292973938</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1760979076287039</v>
       </c>
     </row>
     <row r="11">
@@ -816,28 +944,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9.304376915097237</v>
+        <v>11.80046081542969</v>
       </c>
       <c r="D11" t="n">
-        <v>4.351541485199614</v>
+        <v>2.971259501229719</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9119536399841308</v>
+        <v>0.8726012229919433</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05517050155372261</v>
+        <v>11.80046081542969</v>
       </c>
       <c r="G11" t="n">
-        <v>9.078693464398384</v>
+        <v>2.971259501229719</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9162482500076294</v>
+        <v>0.8726012229919433</v>
       </c>
       <c r="I11" t="n">
-        <v>18.59125047922134</v>
+        <v>0.07966658708770274</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8930045366287231</v>
+        <v>11.23295314610004</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.981353312806007</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8995427846908569</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5675076693296432</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5372347743680608</v>
       </c>
     </row>
   </sheetData>
